--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_301_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_301_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -1727,7 +1727,7 @@
         <v>14</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -2710,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
         <v>5</v>
@@ -2909,10 +2909,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>2</v>
@@ -3491,16 +3491,16 @@
         <v>9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>91</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -4292,7 +4292,7 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4883,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>3</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>4</v>
@@ -5664,7 +5664,7 @@
         <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>15</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>5</v>
@@ -6784,16 +6784,16 @@
         <v>93</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X48" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_301_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_301_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -851,20 +851,20 @@
         <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>96.55</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>3</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>9</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5709,25 +5709,25 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6796,14 +6796,14 @@
         <v>7</v>
       </c>
       <c r="X48" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK48" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
